--- a/doc/性能测试结果.xlsx
+++ b/doc/性能测试结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Horizon\Projects\Ongoing\AI_project\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B470C2D-69CA-441E-BEFA-20F81753DAD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093BA8B7-B636-4713-A69A-AE8A9C2D8139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="31">
   <si>
     <t>实例个数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,6 +122,10 @@
   </si>
   <si>
     <t>后端参数设置：改变MySQL连接池参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>干扰因素</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -187,6 +191,10 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>存在日志和性能监控</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -195,7 +203,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -286,6 +294,12 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -307,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -347,6 +361,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -657,10 +674,14 @@
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
+      <c r="E1" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="G1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="13"/>
       <c r="M1" s="8" t="s">
         <v>22</v>
       </c>
@@ -682,18 +703,20 @@
       </c>
       <c r="D2" s="11"/>
       <c r="E2" s="12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H2" s="13"/>
       <c r="M2" s="9" t="s">
         <v>5</v>
       </c>
       <c r="N2" s="9"/>
-      <c r="O2" s="9"/>
+      <c r="O2" s="9">
+        <v>150</v>
+      </c>
       <c r="P2" s="9"/>
       <c r="Q2" s="9" t="s">
         <v>9</v>
@@ -711,19 +734,21 @@
         <v>12</v>
       </c>
       <c r="D3" s="11"/>
-      <c r="E3" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="13"/>
+      <c r="E3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="7"/>
       <c r="M3" s="9" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
+      <c r="O3" s="9">
+        <v>100</v>
+      </c>
       <c r="P3" s="9"/>
       <c r="Q3" s="9" t="s">
         <v>10</v>
@@ -741,26 +766,30 @@
         <v>12</v>
       </c>
       <c r="D4" s="11"/>
-      <c r="E4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="7"/>
+      <c r="E4" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="12"/>
+      <c r="G4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="11"/>
       <c r="M4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
+      <c r="O4" s="9">
+        <v>20</v>
+      </c>
       <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
+      <c r="Q4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="R4" s="8"/>
       <c r="S4" s="9"/>
       <c r="T4" s="9"/>
     </row>
-    <row r="5" spans="1:20" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>4</v>
       </c>
@@ -770,7 +799,7 @@
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -783,10 +812,12 @@
         <v>8</v>
       </c>
       <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
+      <c r="O5" s="9">
+        <v>500</v>
+      </c>
       <c r="P5" s="9"/>
       <c r="Q5" s="8" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="R5" s="8"/>
       <c r="S5" s="9"/>
@@ -1153,16 +1184,22 @@
       <c r="J17">
         <v>2000</v>
       </c>
+      <c r="K17" s="3">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="L17" s="3">
+        <v>5.6000000000000001E-2</v>
+      </c>
       <c r="M17">
         <v>5</v>
       </c>
       <c r="N17">
         <v>2000</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="3">
         <v>0.04</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="3">
         <v>0.05</v>
       </c>
     </row>
@@ -1197,16 +1234,22 @@
       <c r="J18">
         <v>1000</v>
       </c>
+      <c r="K18" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="L18" s="3">
+        <v>5.2999999999999999E-2</v>
+      </c>
       <c r="M18">
         <v>10</v>
       </c>
       <c r="N18">
         <v>1000</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="3">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="3">
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
@@ -1241,16 +1284,22 @@
       <c r="J19">
         <v>500</v>
       </c>
+      <c r="K19" s="3">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="L19" s="3">
+        <v>7.1999999999999995E-2</v>
+      </c>
       <c r="M19">
         <v>20</v>
       </c>
       <c r="N19">
         <v>500</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="3">
         <v>0.52</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="3">
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
@@ -1285,16 +1334,22 @@
       <c r="J20">
         <v>200</v>
       </c>
+      <c r="K20" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="L20" s="3">
+        <v>0.17799999999999999</v>
+      </c>
       <c r="M20">
         <v>50</v>
       </c>
       <c r="N20">
         <v>200</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="3">
         <v>0.14099999999999999</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="3">
         <v>0.221</v>
       </c>
     </row>
@@ -1329,16 +1384,22 @@
       <c r="J21">
         <v>100</v>
       </c>
+      <c r="K21" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0.26300000000000001</v>
+      </c>
       <c r="M21">
         <v>100</v>
       </c>
       <c r="N21">
         <v>100</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="3">
         <v>0.23</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="3">
         <v>0.34799999999999998</v>
       </c>
     </row>
@@ -1373,16 +1434,22 @@
       <c r="J22">
         <v>50</v>
       </c>
+      <c r="K22" s="3">
+        <v>0.309</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0.49099999999999999</v>
+      </c>
       <c r="M22">
         <v>200</v>
       </c>
       <c r="N22">
         <v>50</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="3">
         <v>0.35699999999999998</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="3">
         <v>0.56799999999999995</v>
       </c>
     </row>
@@ -1417,16 +1484,22 @@
       <c r="J23">
         <v>10</v>
       </c>
+      <c r="K23" s="3">
+        <v>2.5310000000000001</v>
+      </c>
+      <c r="L23" s="3">
+        <v>5.0439999999999996</v>
+      </c>
       <c r="M23">
         <v>1000</v>
       </c>
       <c r="N23">
         <v>10</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="3">
         <v>3.1040000000000001</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="3">
         <v>5.6959999999999997</v>
       </c>
     </row>
@@ -1483,26 +1556,26 @@
         <v>5</v>
       </c>
       <c r="B29" s="11"/>
-      <c r="C29" s="11">
-        <v>500</v>
-      </c>
-      <c r="D29" s="11"/>
+      <c r="C29" s="15">
+        <v>150</v>
+      </c>
+      <c r="D29" s="15"/>
       <c r="E29" s="11" t="s">
         <v>5</v>
       </c>
       <c r="F29" s="11"/>
-      <c r="G29" s="11">
-        <v>375</v>
-      </c>
-      <c r="H29" s="11"/>
+      <c r="G29" s="15">
+        <v>150</v>
+      </c>
+      <c r="H29" s="15"/>
       <c r="I29" s="11" t="s">
         <v>5</v>
       </c>
       <c r="J29" s="11"/>
-      <c r="K29" s="11">
-        <v>125</v>
-      </c>
-      <c r="L29" s="11"/>
+      <c r="K29" s="15">
+        <v>150</v>
+      </c>
+      <c r="L29" s="15"/>
       <c r="M29" s="11"/>
       <c r="N29" s="11"/>
       <c r="O29" s="11"/>
@@ -1513,26 +1586,26 @@
         <v>6</v>
       </c>
       <c r="B30" s="11"/>
-      <c r="C30" s="11">
-        <v>400</v>
-      </c>
-      <c r="D30" s="11"/>
+      <c r="C30" s="15">
+        <v>100</v>
+      </c>
+      <c r="D30" s="15"/>
       <c r="E30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="F30" s="11"/>
-      <c r="G30" s="11">
-        <v>300</v>
-      </c>
-      <c r="H30" s="11"/>
+      <c r="G30" s="15">
+        <v>100</v>
+      </c>
+      <c r="H30" s="15"/>
       <c r="I30" s="11" t="s">
         <v>6</v>
       </c>
       <c r="J30" s="11"/>
-      <c r="K30" s="11">
+      <c r="K30" s="15">
         <v>100</v>
       </c>
-      <c r="L30" s="11"/>
+      <c r="L30" s="15"/>
       <c r="M30" s="11"/>
       <c r="N30" s="11"/>
       <c r="O30" s="11"/>
@@ -1543,26 +1616,26 @@
         <v>7</v>
       </c>
       <c r="B31" s="11"/>
-      <c r="C31" s="11">
-        <v>50</v>
-      </c>
-      <c r="D31" s="11"/>
+      <c r="C31" s="15">
+        <v>20</v>
+      </c>
+      <c r="D31" s="15"/>
       <c r="E31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="F31" s="11"/>
-      <c r="G31" s="11">
-        <v>37</v>
-      </c>
-      <c r="H31" s="11"/>
+      <c r="G31" s="15">
+        <v>20</v>
+      </c>
+      <c r="H31" s="15"/>
       <c r="I31" s="11" t="s">
         <v>7</v>
       </c>
       <c r="J31" s="11"/>
-      <c r="K31" s="11">
-        <v>12</v>
-      </c>
-      <c r="L31" s="11"/>
+      <c r="K31" s="15">
+        <v>20</v>
+      </c>
+      <c r="L31" s="15"/>
       <c r="M31" s="11"/>
       <c r="N31" s="11"/>
       <c r="O31" s="11"/>
@@ -1573,26 +1646,26 @@
         <v>8</v>
       </c>
       <c r="B32" s="11"/>
-      <c r="C32" s="11">
-        <v>5000</v>
-      </c>
-      <c r="D32" s="11"/>
+      <c r="C32" s="15">
+        <v>500</v>
+      </c>
+      <c r="D32" s="15"/>
       <c r="E32" s="11" t="s">
         <v>8</v>
       </c>
       <c r="F32" s="11"/>
-      <c r="G32" s="11">
+      <c r="G32" s="15">
         <v>500</v>
       </c>
-      <c r="H32" s="11"/>
+      <c r="H32" s="15"/>
       <c r="I32" s="11" t="s">
         <v>8</v>
       </c>
       <c r="J32" s="11"/>
-      <c r="K32" s="11">
+      <c r="K32" s="15">
         <v>500</v>
       </c>
-      <c r="L32" s="11"/>
+      <c r="L32" s="15"/>
       <c r="M32" s="11"/>
       <c r="N32" s="11"/>
       <c r="O32" s="11"/>
@@ -1636,7 +1709,7 @@
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="H34" s="10"/>
       <c r="I34" s="10" t="s">
@@ -1644,7 +1717,7 @@
       </c>
       <c r="J34" s="10"/>
       <c r="K34" s="10">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
@@ -1666,7 +1739,7 @@
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="10">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H35" s="10"/>
       <c r="I35" s="10" t="s">
@@ -1674,7 +1747,7 @@
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
@@ -1731,6 +1804,12 @@
       <c r="B38">
         <v>2000</v>
       </c>
+      <c r="C38" s="3">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="D38" s="3">
+        <v>5.6000000000000001E-2</v>
+      </c>
       <c r="E38">
         <v>5</v>
       </c>
@@ -1750,6 +1829,12 @@
       </c>
       <c r="B39">
         <v>1000</v>
+      </c>
+      <c r="C39" s="3">
+        <v>3.9E-2</v>
+      </c>
+      <c r="D39" s="3">
+        <v>5.2999999999999999E-2</v>
       </c>
       <c r="E39">
         <v>10</v>
@@ -1771,6 +1856,12 @@
       <c r="B40">
         <v>500</v>
       </c>
+      <c r="C40" s="3">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="D40" s="3">
+        <v>7.1999999999999995E-2</v>
+      </c>
       <c r="E40">
         <v>20</v>
       </c>
@@ -1791,6 +1882,12 @@
       <c r="B41">
         <v>200</v>
       </c>
+      <c r="C41" s="3">
+        <v>0.115</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.17799999999999999</v>
+      </c>
       <c r="E41">
         <v>50</v>
       </c>
@@ -1811,6 +1908,12 @@
       <c r="B42">
         <v>100</v>
       </c>
+      <c r="C42" s="3">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.26300000000000001</v>
+      </c>
       <c r="E42">
         <v>100</v>
       </c>
@@ -1831,6 +1934,12 @@
       <c r="B43">
         <v>50</v>
       </c>
+      <c r="C43" s="3">
+        <v>0.309</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.49099999999999999</v>
+      </c>
       <c r="E43">
         <v>200</v>
       </c>
@@ -1850,6 +1959,12 @@
       </c>
       <c r="B44">
         <v>10</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2.5310000000000001</v>
+      </c>
+      <c r="D44" s="3">
+        <v>5.0439999999999996</v>
       </c>
       <c r="E44">
         <v>1000</v>
@@ -2029,12 +2144,15 @@
       <c r="L58" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="197">
+  <mergeCells count="198">
     <mergeCell ref="K8:L8"/>
     <mergeCell ref="K9:L9"/>
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="A27:L27"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="Q5:R5"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="O35:P35"/>
     <mergeCell ref="Q49:T49"/>
@@ -2077,7 +2195,6 @@
     <mergeCell ref="M8:N8"/>
     <mergeCell ref="M9:N9"/>
     <mergeCell ref="A6:P6"/>
-    <mergeCell ref="E1:H1"/>
     <mergeCell ref="G8:H8"/>
     <mergeCell ref="E9:F9"/>
     <mergeCell ref="A1:D1"/>
@@ -2134,8 +2251,8 @@
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="E34:F34"/>
     <mergeCell ref="G34:H34"/>
+    <mergeCell ref="K32:L32"/>
     <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
     <mergeCell ref="A33:D33"/>
     <mergeCell ref="E33:H33"/>
     <mergeCell ref="I33:L33"/>
@@ -2204,9 +2321,9 @@
     <mergeCell ref="C11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="Q5:R5"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="Q4:R4"/>
     <mergeCell ref="S5:T5"/>
     <mergeCell ref="S3:T3"/>
     <mergeCell ref="S2:T2"/>
@@ -2221,12 +2338,11 @@
     <mergeCell ref="O2:P2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="E5:L5"/>
-    <mergeCell ref="Q4:R4"/>
     <mergeCell ref="S4:T4"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/性能测试结果.xlsx
+++ b/doc/性能测试结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Horizon\Projects\Ongoing\AI_project\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{093BA8B7-B636-4713-A69A-AE8A9C2D8139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE48B527-CC54-4455-99D7-22F6D80336EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
   <si>
     <t>实例个数</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -126,10 +126,6 @@
   </si>
   <si>
     <t>干扰因素</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最优并发数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -203,7 +199,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,6 +296,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -321,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -362,6 +371,12 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -735,11 +750,11 @@
       </c>
       <c r="D3" s="11"/>
       <c r="E3" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H3" s="7"/>
       <c r="M3" s="9" t="s">
@@ -771,7 +786,7 @@
       </c>
       <c r="F4" s="12"/>
       <c r="G4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H4" s="11"/>
       <c r="M4" s="9" t="s">
@@ -782,12 +797,14 @@
         <v>20</v>
       </c>
       <c r="P4" s="9"/>
-      <c r="Q4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="R4" s="8"/>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9"/>
+      <c r="Q4" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="17"/>
+      <c r="S4" s="16">
+        <v>12</v>
+      </c>
+      <c r="T4" s="16"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
@@ -799,7 +816,7 @@
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -816,12 +833,14 @@
         <v>500</v>
       </c>
       <c r="P5" s="9"/>
-      <c r="Q5" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="R5" s="8"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
+      <c r="Q5" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="R5" s="17"/>
+      <c r="S5" s="16">
+        <v>12</v>
+      </c>
+      <c r="T5" s="16"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
@@ -1747,7 +1766,7 @@
       </c>
       <c r="J35" s="10"/>
       <c r="K35" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L35" s="10"/>
       <c r="M35" s="10"/>
@@ -1816,6 +1835,12 @@
       <c r="F38">
         <v>2000</v>
       </c>
+      <c r="G38">
+        <v>3.9E-2</v>
+      </c>
+      <c r="H38">
+        <v>5.1999999999999998E-2</v>
+      </c>
       <c r="I38">
         <v>5</v>
       </c>
@@ -1842,6 +1867,12 @@
       <c r="F39">
         <v>1000</v>
       </c>
+      <c r="G39">
+        <v>3.9E-2</v>
+      </c>
+      <c r="H39">
+        <v>4.9000000000000002E-2</v>
+      </c>
       <c r="I39">
         <v>10</v>
       </c>
@@ -1868,6 +1899,12 @@
       <c r="F40">
         <v>500</v>
       </c>
+      <c r="G40">
+        <v>4.9000000000000002E-2</v>
+      </c>
+      <c r="H40">
+        <v>7.1999999999999995E-2</v>
+      </c>
       <c r="I40">
         <v>20</v>
       </c>
@@ -1894,6 +1931,12 @@
       <c r="F41">
         <v>200</v>
       </c>
+      <c r="G41">
+        <v>0.113</v>
+      </c>
+      <c r="H41">
+        <v>0.17599999999999999</v>
+      </c>
       <c r="I41">
         <v>50</v>
       </c>
@@ -1920,6 +1963,12 @@
       <c r="F42">
         <v>100</v>
       </c>
+      <c r="G42">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="H42">
+        <v>0.27500000000000002</v>
+      </c>
       <c r="I42">
         <v>100</v>
       </c>
@@ -1946,6 +1995,12 @@
       <c r="F43">
         <v>50</v>
       </c>
+      <c r="G43">
+        <v>0.317</v>
+      </c>
+      <c r="H43">
+        <v>0.51800000000000002</v>
+      </c>
       <c r="I43">
         <v>200</v>
       </c>
@@ -1971,6 +2026,12 @@
       </c>
       <c r="F44">
         <v>10</v>
+      </c>
+      <c r="G44">
+        <v>2.5409999999999999</v>
+      </c>
+      <c r="H44">
+        <v>4.6079999999999997</v>
       </c>
       <c r="I44">
         <v>1000</v>
@@ -2346,6 +2407,7 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/doc/性能测试结果.xlsx
+++ b/doc/性能测试结果.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Horizon\Projects\Ongoing\AI_project\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{739BB38B-73F8-497E-9E2E-0846D24962E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719BD8B0-53A3-424F-A876-68A855B0BF8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,11 +212,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>33s</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>35s</t>
+    <t>26s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>25s</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -373,6 +373,32 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -382,38 +408,12 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -718,374 +718,374 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="15" t="s">
+      <c r="F1" s="11"/>
+      <c r="G1" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="15"/>
+      <c r="H1" s="20"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="14" t="s">
+      <c r="D2" s="12"/>
+      <c r="E2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="15" t="s">
+      <c r="F2" s="11"/>
+      <c r="G2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="H2" s="15"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="13">
+      <c r="B3" s="14"/>
+      <c r="C3" s="12">
         <v>12</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="6" t="s">
+      <c r="D3" s="12"/>
+      <c r="E3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="8" t="s">
+      <c r="F3" s="17"/>
+      <c r="G3" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="9"/>
+      <c r="H3" s="14"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="13">
+      <c r="B4" s="14"/>
+      <c r="C4" s="12">
         <v>12</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="14" t="s">
+      <c r="D4" s="12"/>
+      <c r="E4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="14"/>
-      <c r="G4" s="13" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="13"/>
+      <c r="H4" s="12"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A5" s="9" t="s">
+      <c r="A5" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="13">
+      <c r="B5" s="14"/>
+      <c r="C5" s="12">
         <v>2</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12" t="s">
+      <c r="B7" s="10"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12" t="s">
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="12"/>
-      <c r="K7" s="12"/>
-      <c r="L7" s="12"/>
-      <c r="M7" s="12" t="s">
+      <c r="J7" s="10"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12">
+      <c r="B8" s="10"/>
+      <c r="C8" s="10">
         <v>500</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12">
+      <c r="F8" s="10"/>
+      <c r="G8" s="10">
         <v>250</v>
       </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12" t="s">
+      <c r="H8" s="10"/>
+      <c r="I8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="12">
+      <c r="J8" s="10"/>
+      <c r="K8" s="10">
         <v>150</v>
       </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12" t="s">
+      <c r="L8" s="10"/>
+      <c r="M8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12">
+      <c r="N8" s="10"/>
+      <c r="O8" s="10">
         <v>100</v>
       </c>
-      <c r="P8" s="12"/>
+      <c r="P8" s="10"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12">
+      <c r="B9" s="10"/>
+      <c r="C9" s="10">
         <v>400</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12" t="s">
+      <c r="D9" s="10"/>
+      <c r="E9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12">
+      <c r="F9" s="10"/>
+      <c r="G9" s="10">
         <v>200</v>
       </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12" t="s">
+      <c r="H9" s="10"/>
+      <c r="I9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="12">
+      <c r="J9" s="10"/>
+      <c r="K9" s="10">
         <v>100</v>
       </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12" t="s">
+      <c r="L9" s="10"/>
+      <c r="M9" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12">
+      <c r="N9" s="10"/>
+      <c r="O9" s="10">
         <v>25</v>
       </c>
-      <c r="P9" s="12"/>
+      <c r="P9" s="10"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12">
+      <c r="B10" s="10"/>
+      <c r="C10" s="10">
         <v>50</v>
       </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12">
+      <c r="F10" s="10"/>
+      <c r="G10" s="10">
         <v>25</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12" t="s">
+      <c r="H10" s="10"/>
+      <c r="I10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J10" s="12"/>
-      <c r="K10" s="12">
+      <c r="J10" s="10"/>
+      <c r="K10" s="10">
         <v>20</v>
       </c>
-      <c r="L10" s="12"/>
-      <c r="M10" s="12" t="s">
+      <c r="L10" s="10"/>
+      <c r="M10" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="12">
+      <c r="N10" s="10"/>
+      <c r="O10" s="10">
         <v>6</v>
       </c>
-      <c r="P10" s="12"/>
+      <c r="P10" s="10"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10">
         <v>5000</v>
       </c>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12" t="s">
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12">
+      <c r="F11" s="10"/>
+      <c r="G11" s="10">
         <v>1000</v>
       </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12" t="s">
+      <c r="H11" s="10"/>
+      <c r="I11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="12"/>
-      <c r="K11" s="12">
+      <c r="J11" s="10"/>
+      <c r="K11" s="10">
         <v>500</v>
       </c>
-      <c r="L11" s="12"/>
-      <c r="M11" s="12" t="s">
+      <c r="L11" s="10"/>
+      <c r="M11" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="12">
+      <c r="N11" s="10"/>
+      <c r="O11" s="10">
         <v>250</v>
       </c>
-      <c r="P11" s="12"/>
+      <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="13"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13" t="s">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13" t="s">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13" t="s">
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="13"/>
-      <c r="C13" s="13">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12">
         <v>100</v>
       </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13" t="s">
+      <c r="D13" s="12"/>
+      <c r="E13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12">
         <v>100</v>
       </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13" t="s">
+      <c r="H13" s="12"/>
+      <c r="I13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13">
+      <c r="J13" s="12"/>
+      <c r="K13" s="12">
         <v>100</v>
       </c>
-      <c r="L13" s="13"/>
-      <c r="M13" s="13" t="s">
+      <c r="L13" s="12"/>
+      <c r="M13" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="N13" s="13"/>
-      <c r="O13" s="13">
+      <c r="N13" s="12"/>
+      <c r="O13" s="12">
         <v>100</v>
       </c>
-      <c r="P13" s="13"/>
+      <c r="P13" s="12"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13">
-        <v>10</v>
-      </c>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13">
-        <v>10</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13">
-        <v>10</v>
-      </c>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13">
-        <v>10</v>
-      </c>
-      <c r="P14" s="13"/>
+      <c r="A14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12">
+        <v>10</v>
+      </c>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12">
+        <v>10</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12">
+        <v>10</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12">
+        <v>10</v>
+      </c>
+      <c r="P14" s="12"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1488,216 +1488,216 @@
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A25" s="14" t="s">
+      <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="13"/>
-      <c r="C26" s="13"/>
-      <c r="D26" s="13"/>
-      <c r="E26" s="13" t="s">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13" t="s">
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J26" s="13"/>
-      <c r="K26" s="13"/>
-      <c r="L26" s="13"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A27" s="13" t="s">
+      <c r="A27" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="13"/>
-      <c r="C27" s="17">
+      <c r="B27" s="12"/>
+      <c r="C27" s="15">
         <v>150</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="13" t="s">
+      <c r="D27" s="15"/>
+      <c r="E27" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="17">
+      <c r="F27" s="12"/>
+      <c r="G27" s="15">
         <v>150</v>
       </c>
-      <c r="H27" s="17"/>
-      <c r="I27" s="13" t="s">
+      <c r="H27" s="15"/>
+      <c r="I27" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="J27" s="13"/>
-      <c r="K27" s="17">
+      <c r="J27" s="12"/>
+      <c r="K27" s="15">
         <v>150</v>
       </c>
-      <c r="L27" s="17"/>
+      <c r="L27" s="15"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
+      <c r="A28" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B28" s="13"/>
-      <c r="C28" s="17">
+      <c r="B28" s="12"/>
+      <c r="C28" s="15">
         <v>100</v>
       </c>
-      <c r="D28" s="17"/>
-      <c r="E28" s="13" t="s">
+      <c r="D28" s="15"/>
+      <c r="E28" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="17">
+      <c r="F28" s="12"/>
+      <c r="G28" s="15">
         <v>100</v>
       </c>
-      <c r="H28" s="17"/>
-      <c r="I28" s="13" t="s">
+      <c r="H28" s="15"/>
+      <c r="I28" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="J28" s="13"/>
-      <c r="K28" s="17">
+      <c r="J28" s="12"/>
+      <c r="K28" s="15">
         <v>100</v>
       </c>
-      <c r="L28" s="17"/>
+      <c r="L28" s="15"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="17">
+      <c r="B29" s="12"/>
+      <c r="C29" s="15">
         <v>20</v>
       </c>
-      <c r="D29" s="17"/>
-      <c r="E29" s="13" t="s">
+      <c r="D29" s="15"/>
+      <c r="E29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="13"/>
-      <c r="G29" s="17">
+      <c r="F29" s="12"/>
+      <c r="G29" s="15">
         <v>20</v>
       </c>
-      <c r="H29" s="17"/>
-      <c r="I29" s="13" t="s">
+      <c r="H29" s="15"/>
+      <c r="I29" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J29" s="13"/>
-      <c r="K29" s="17">
+      <c r="J29" s="12"/>
+      <c r="K29" s="15">
         <v>20</v>
       </c>
-      <c r="L29" s="17"/>
+      <c r="L29" s="15"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="17">
+      <c r="B30" s="12"/>
+      <c r="C30" s="15">
         <v>500</v>
       </c>
-      <c r="D30" s="17"/>
-      <c r="E30" s="13" t="s">
+      <c r="D30" s="15"/>
+      <c r="E30" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="13"/>
-      <c r="G30" s="17">
+      <c r="F30" s="12"/>
+      <c r="G30" s="15">
         <v>500</v>
       </c>
-      <c r="H30" s="17"/>
-      <c r="I30" s="13" t="s">
+      <c r="H30" s="15"/>
+      <c r="I30" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="J30" s="13"/>
-      <c r="K30" s="17">
+      <c r="J30" s="12"/>
+      <c r="K30" s="15">
         <v>500</v>
       </c>
-      <c r="L30" s="17"/>
+      <c r="L30" s="15"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A31" s="12" t="s">
+      <c r="A31" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12" t="s">
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12" t="s">
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A32" s="12" t="s">
+      <c r="A32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B32" s="12"/>
-      <c r="C32" s="12">
+      <c r="B32" s="10"/>
+      <c r="C32" s="10">
         <v>100</v>
       </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12" t="s">
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12">
+      <c r="F32" s="10"/>
+      <c r="G32" s="10">
         <v>50</v>
       </c>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12" t="s">
+      <c r="H32" s="10"/>
+      <c r="I32" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12">
+      <c r="J32" s="10"/>
+      <c r="K32" s="10">
         <v>25</v>
       </c>
-      <c r="L32" s="12"/>
+      <c r="L32" s="10"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A33" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B33" s="12"/>
-      <c r="C33" s="12">
-        <v>10</v>
-      </c>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12">
+      <c r="A33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10">
+        <v>10</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10">
         <v>5</v>
       </c>
-      <c r="H33" s="12"/>
-      <c r="I33" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J33" s="12"/>
-      <c r="K33" s="12">
+      <c r="H33" s="10"/>
+      <c r="I33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J33" s="10"/>
+      <c r="K33" s="10">
         <v>4</v>
       </c>
-      <c r="L33" s="12"/>
+      <c r="L33" s="10"/>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
@@ -1996,90 +1996,96 @@
       <c r="J42">
         <v>10</v>
       </c>
+      <c r="K42">
+        <v>2.6080000000000001</v>
+      </c>
+      <c r="L42">
+        <v>5.0750000000000002</v>
+      </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A44" s="10" t="s">
+      <c r="A44" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B44" s="10"/>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="8"/>
+      <c r="D44" s="8"/>
+      <c r="E44" s="8"/>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="8"/>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="11">
+      <c r="B45" s="9"/>
+      <c r="C45" s="9">
         <v>150</v>
       </c>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11" t="s">
+      <c r="D45" s="9"/>
+      <c r="E45" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11">
-        <v>25</v>
-      </c>
-      <c r="H45" s="11"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9">
+        <v>50</v>
+      </c>
+      <c r="H45" s="9"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11">
+      <c r="B46" s="9"/>
+      <c r="C46" s="9">
         <v>100</v>
       </c>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11">
-        <v>4</v>
-      </c>
-      <c r="H46" s="11"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9">
+        <v>5</v>
+      </c>
+      <c r="H46" s="9"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="11">
+      <c r="B47" s="9"/>
+      <c r="C47" s="9">
         <v>20</v>
       </c>
-      <c r="D47" s="11"/>
-      <c r="E47" s="19" t="s">
+      <c r="D47" s="9"/>
+      <c r="E47" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F47" s="19"/>
-      <c r="G47" s="18">
+      <c r="F47" s="13"/>
+      <c r="G47" s="19">
         <v>12</v>
       </c>
-      <c r="H47" s="18"/>
+      <c r="H47" s="19"/>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11">
+      <c r="B48" s="9"/>
+      <c r="C48" s="9">
         <v>500</v>
       </c>
-      <c r="D48" s="11"/>
-      <c r="E48" s="19" t="s">
+      <c r="D48" s="9"/>
+      <c r="E48" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="F48" s="19"/>
-      <c r="G48" s="18">
+      <c r="F48" s="13"/>
+      <c r="G48" s="19">
         <v>12</v>
       </c>
-      <c r="H48" s="18"/>
+      <c r="H48" s="19"/>
       <c r="I48" s="1"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
@@ -2089,10 +2095,10 @@
       <c r="O48" s="1"/>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A49" s="13"/>
-      <c r="B49" s="13"/>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
+      <c r="A49" s="12"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="12"/>
+      <c r="D49" s="12"/>
       <c r="I49" s="3"/>
       <c r="J49" s="3"/>
       <c r="K49" s="3"/>
@@ -2108,10 +2114,10 @@
       <c r="B50" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D50" s="10"/>
+      <c r="D50" s="8"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
@@ -2121,112 +2127,112 @@
       <c r="O50" s="3"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A51" s="20">
+      <c r="A51" s="7">
         <v>5</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="7">
         <v>2000</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="D51" s="11"/>
+      <c r="D51" s="9"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A52" s="20">
-        <v>10</v>
-      </c>
-      <c r="B52" s="20">
+      <c r="A52" s="7">
+        <v>10</v>
+      </c>
+      <c r="B52" s="7">
         <v>1000</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D52" s="11"/>
+      <c r="D52" s="9"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A53" s="20">
+      <c r="A53" s="7">
         <v>20</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="7">
         <v>500</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="D53" s="11"/>
+      <c r="D53" s="9"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A54" s="20">
+      <c r="A54" s="7">
         <v>50</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="7">
         <v>200</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D54" s="11"/>
+      <c r="D54" s="9"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A55" s="20">
+      <c r="A55" s="7">
         <v>100</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="7">
         <v>100</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="D55" s="11"/>
+      <c r="D55" s="9"/>
       <c r="I55" s="3"/>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A56" s="20">
+      <c r="A56" s="7">
         <v>200</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="7">
         <v>50</v>
       </c>
-      <c r="C56" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D56" s="11"/>
+      <c r="C56" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" s="9"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A57" s="20">
+      <c r="A57" s="7">
         <v>1000</v>
       </c>
-      <c r="B57" s="20">
-        <v>10</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D57" s="11"/>
+      <c r="B57" s="7">
+        <v>10</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="9"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.2">
       <c r="I58" s="1"/>
@@ -2236,6 +2242,127 @@
     </row>
   </sheetData>
   <mergeCells count="145">
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="C47:D47"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="E5:L5"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="O10:P10"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="O11:P11"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:P9"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:P12"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="E32:F32"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="E31:H31"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="E33:F33"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="I31:L31"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="E7:H7"/>
+    <mergeCell ref="I7:L7"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="C50:D50"/>
     <mergeCell ref="C51:D51"/>
     <mergeCell ref="C52:D52"/>
@@ -2249,63 +2376,6 @@
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="K11:L11"/>
     <mergeCell ref="A25:L25"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="E48:F48"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:P12"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="E31:H31"/>
-    <mergeCell ref="I31:L31"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="G30:H30"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="E7:H7"/>
-    <mergeCell ref="I7:L7"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="E12:H12"/>
     <mergeCell ref="I12:L12"/>
     <mergeCell ref="A26:D26"/>
@@ -2317,70 +2387,6 @@
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="G27:H27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="G28:H28"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="O10:P10"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="O11:P11"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="O8:P8"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:P9"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E47:F47"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="E45:F45"/>
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C47:D47"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="E5:L5"/>
-    <mergeCell ref="G47:H47"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2394,130 +2400,130 @@
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A1" s="14"/>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
-      <c r="O1" s="14"/>
-      <c r="P1" s="14"/>
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+      <c r="O2" s="12"/>
+      <c r="P2" s="12"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13"/>
-      <c r="P3" s="13"/>
+      <c r="A3" s="12"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="12"/>
+      <c r="K3" s="12"/>
+      <c r="L3" s="12"/>
+      <c r="M3" s="12"/>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
@@ -2557,6 +2563,46 @@
     </row>
   </sheetData>
   <mergeCells count="52">
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="O5:P5"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="C2:D2"/>
@@ -2569,46 +2615,6 @@
     <mergeCell ref="I1:L1"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="O3:P3"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
